--- a/histograms/histogram_Calc_time__h_.xlsx
+++ b/histograms/histogram_Calc_time__h_.xlsx
@@ -445,7 +445,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>4622</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="n">
-        <v>16052</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>25</v>
       </c>
       <c r="B4" t="n">
-        <v>2871</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>35</v>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>1652</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>55</v>
       </c>
       <c r="B7" t="n">
-        <v>603</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>65</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>75</v>
       </c>
       <c r="B9" t="n">
-        <v>107</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -541,7 +541,7 @@
         <v>125</v>
       </c>
       <c r="B14" t="n">
-        <v>92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -597,7 +597,7 @@
         <v>195</v>
       </c>
       <c r="B21" t="n">
-        <v>295</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
